--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136007787</v>
+        <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>83341</v>
+        <v>79562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,37 +1252,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750899</v>
+        <v>751049</v>
       </c>
       <c r="R7" t="n">
-        <v>7520119</v>
+        <v>7520222</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,22 +1306,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,31 +1322,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007787</t>
+          <t>https://artportalen.se/Sighting/137111952</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136007580</v>
+        <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>89334</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,40 +1359,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4412</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750682</v>
+        <v>750941</v>
       </c>
       <c r="R8" t="n">
-        <v>7520114</v>
+        <v>7520399</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,22 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,34 +1427,38 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007580</t>
+          <t>https://artportalen.se/Sighting/137111948</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136007581</v>
+        <v>136007787</v>
       </c>
       <c r="B9" t="n">
-        <v>89334</v>
+        <v>83341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,40 +1466,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Honkamettä, T lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750804</v>
+        <v>750899</v>
       </c>
       <c r="R9" t="n">
-        <v>7520071</v>
+        <v>7520119</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,34 +1544,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007581</t>
+          <t>https://artportalen.se/Sighting/136007787</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136007582</v>
+        <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>89334</v>
+        <v>93450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,40 +1578,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750826</v>
+        <v>751061</v>
       </c>
       <c r="R10" t="n">
-        <v>7520150</v>
+        <v>7520219</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,22 +1632,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,34 +1646,38 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007582</t>
+          <t>https://artportalen.se/Sighting/137111950</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136007770</v>
+        <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>89334</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,37 +1685,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751130</v>
+        <v>751049</v>
       </c>
       <c r="R11" t="n">
-        <v>7520178</v>
+        <v>7520203</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,22 +1739,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,28 +1755,33 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007770</t>
+          <t>https://artportalen.se/Sighting/137111951</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136007773</v>
+        <v>136007580</v>
       </c>
       <c r="B12" t="n">
         <v>89334</v>
@@ -1842,19 +1810,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751104</v>
+        <v>750682</v>
       </c>
       <c r="R12" t="n">
-        <v>7520161</v>
+        <v>7520114</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,30 +1873,31 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007773</t>
+          <t>https://artportalen.se/Sighting/136007580</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136007791</v>
+        <v>136007581</v>
       </c>
       <c r="B13" t="n">
         <v>89334</v>
@@ -1954,19 +1926,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750789</v>
+        <v>750804</v>
       </c>
       <c r="R13" t="n">
-        <v>7520067</v>
+        <v>7520071</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,30 +1989,31 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007791</t>
+          <t>https://artportalen.se/Sighting/136007581</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136007803</v>
+        <v>136007582</v>
       </c>
       <c r="B14" t="n">
         <v>89334</v>
@@ -2066,19 +2042,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750825</v>
+        <v>750826</v>
       </c>
       <c r="R14" t="n">
-        <v>7520296</v>
+        <v>7520150</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,30 +2105,31 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007803</t>
+          <t>https://artportalen.se/Sighting/136007582</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136007810</v>
+        <v>136007770</v>
       </c>
       <c r="B15" t="n">
         <v>89334</v>
@@ -2184,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751192</v>
+        <v>751130</v>
       </c>
       <c r="R15" t="n">
-        <v>7520403</v>
+        <v>7520178</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2219,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,16 +2235,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007810</t>
+          <t>https://artportalen.se/Sighting/136007770</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136007785</v>
+        <v>136007773</v>
       </c>
       <c r="B16" t="n">
-        <v>78877</v>
+        <v>89334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,21 +2252,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>4412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750899</v>
+        <v>751104</v>
       </c>
       <c r="R16" t="n">
-        <v>7520104</v>
+        <v>7520161</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2321,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,16 +2347,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007785</t>
+          <t>https://artportalen.se/Sighting/136007773</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136007781</v>
+        <v>136007791</v>
       </c>
       <c r="B17" t="n">
-        <v>79231</v>
+        <v>89334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,21 +2364,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,13 +2388,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750992</v>
+        <v>750789</v>
       </c>
       <c r="R17" t="n">
-        <v>7520185</v>
+        <v>7520067</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,16 +2459,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007781</t>
+          <t>https://artportalen.se/Sighting/136007791</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136007808</v>
+        <v>136007803</v>
       </c>
       <c r="B18" t="n">
-        <v>79231</v>
+        <v>89334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,21 +2476,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,13 +2500,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751059</v>
+        <v>750825</v>
       </c>
       <c r="R18" t="n">
-        <v>7520402</v>
+        <v>7520296</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2535,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2545,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,16 +2571,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007808</t>
+          <t>https://artportalen.se/Sighting/136007803</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136007775</v>
+        <v>136007810</v>
       </c>
       <c r="B19" t="n">
-        <v>80093</v>
+        <v>89334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,21 +2588,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,13 +2612,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751051</v>
+        <v>751192</v>
       </c>
       <c r="R19" t="n">
-        <v>7520200</v>
+        <v>7520403</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,7 +2647,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2657,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,16 +2683,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007775</t>
+          <t>https://artportalen.se/Sighting/136007810</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136007780</v>
+        <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>80093</v>
+        <v>89343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2720,37 +2700,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750992</v>
+        <v>751115</v>
       </c>
       <c r="R20" t="n">
-        <v>7520185</v>
+        <v>7520182</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,22 +2754,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2800,69 +2770,74 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007780</t>
+          <t>https://artportalen.se/Sighting/137111955</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136007814</v>
+        <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>80093</v>
+        <v>92081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751215</v>
+        <v>750988</v>
       </c>
       <c r="R21" t="n">
-        <v>7520374</v>
+        <v>7520407</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2886,22 +2861,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,31 +2877,36 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007814</t>
+          <t>https://artportalen.se/Sighting/137111958</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136007786</v>
+        <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>78478</v>
+        <v>92784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,37 +2914,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>5454</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750898</v>
+        <v>750729</v>
       </c>
       <c r="R22" t="n">
-        <v>7520118</v>
+        <v>7520344</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2998,22 +2968,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,34 +2982,38 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007786</t>
+          <t>https://artportalen.se/Sighting/137111947</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136007802</v>
+        <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>58870</v>
+        <v>91472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,34 +3021,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208249</v>
+        <v>5685</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Honkamettä, T lm</t>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750796</v>
+        <v>750749</v>
       </c>
       <c r="R23" t="n">
-        <v>7520094</v>
+        <v>7520486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,22 +3075,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,22 +3091,1673 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137111942</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136007785</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>750899</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7520104</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007785</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137111954</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78886</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>751099</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7520334</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111954</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136007781</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79231</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>750992</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7520185</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007781</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136007808</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79231</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>751059</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7520402</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007808</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136007775</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80093</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>751051</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7520200</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007775</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136007780</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80093</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>750992</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7520185</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007780</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136007814</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80093</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>751215</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7520374</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007814</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137111945</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80102</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>750751</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7520468</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111945</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137111957</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80102</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>751056</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7520217</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111957</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136007786</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78478</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>750898</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7520118</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007786</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137111943</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>751082</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7520185</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111943</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136007802</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58870</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Honkamettä, T lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>750796</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7520094</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136007802</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137111953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79241</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>751083</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7520401</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111953</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137111946</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80073</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>750736</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7520472</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111946</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137111944</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Naturskog NV om Bergsmannijärvi, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>751047</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7520219</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Äldre tallskog på blockig morän med inslag av lövträd och gran, mager miljö</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137111944</t>
         </is>
       </c>
     </row>
@@ -3180,6 +4785,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93450</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91478</v>
+        <v>91482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93460</v>
+        <v>93462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>92796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93462</v>
+        <v>93475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92796</v>
+        <v>92809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92809</v>
+        <v>92811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92811</v>
+        <v>92814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93479</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92814</v>
+        <v>92824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91502</v>
+        <v>91512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>137111943</v>
       </c>
       <c r="B34" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92824</v>
+        <v>92825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93490</v>
+        <v>93495</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89384</v>
+        <v>89387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92825</v>
+        <v>92828</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93495</v>
+        <v>93497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92828</v>
+        <v>92830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93497</v>
+        <v>93503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92830</v>
+        <v>92835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93503</v>
+        <v>93515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89392</v>
+        <v>89403</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93515</v>
+        <v>93516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92847</v>
+        <v>92848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93516</v>
+        <v>93519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89404</v>
+        <v>89407</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92848</v>
+        <v>92851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>137111952</v>
       </c>
       <c r="B7" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137111948</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>137111950</v>
       </c>
       <c r="B10" t="n">
-        <v>93519</v>
+        <v>93523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>137111951</v>
       </c>
       <c r="B11" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137111955</v>
       </c>
       <c r="B20" t="n">
-        <v>89407</v>
+        <v>89411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137111958</v>
       </c>
       <c r="B21" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137111947</v>
       </c>
       <c r="B22" t="n">
-        <v>92851</v>
+        <v>92855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137111942</v>
       </c>
       <c r="B23" t="n">
-        <v>91539</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>137111954</v>
       </c>
       <c r="B25" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137111945</v>
       </c>
       <c r="B31" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>137111957</v>
       </c>
       <c r="B32" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>137111953</v>
       </c>
       <c r="B36" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137111946</v>
       </c>
       <c r="B37" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137111944</v>
       </c>
       <c r="B38" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
